--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136766364</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136766506</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136766616</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136766700</v>
       </c>
       <c r="B14" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136766761</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136766788</v>
       </c>
       <c r="B16" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136767108</v>
       </c>
       <c r="B17" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136767179</v>
       </c>
       <c r="B18" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136767358</v>
       </c>
       <c r="B19" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136767691</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136766364</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136766506</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>136766616</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>136766700</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>136766761</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2301,7 +2301,7 @@
         <v>136766788</v>
       </c>
       <c r="B16" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>136767108</v>
       </c>
       <c r="B17" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>136767179</v>
       </c>
       <c r="B18" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
         <v>136767358</v>
       </c>
       <c r="B19" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>136767691</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -1717,11 +1717,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -1839,11 +1835,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -1961,11 +1953,7 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2083,11 +2071,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2205,11 +2189,7 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2327,11 +2307,7 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2449,11 +2425,7 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2571,11 +2543,7 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2693,11 +2661,7 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sanna, Sanna, Ång</t>
@@ -2815,11 +2779,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Silsjön, Silsjön, Ång</t>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136766364</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136766506</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136766616</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136766700</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>136766761</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136766788</v>
       </c>
       <c r="B16" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136767108</v>
       </c>
       <c r="B17" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136767179</v>
       </c>
       <c r="B18" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>136767358</v>
       </c>
       <c r="B19" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>136767691</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136766733</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136767097</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136767262</v>
       </c>
       <c r="B7" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136767385</v>
       </c>
       <c r="B8" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136767422</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136767654</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136766364</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>136766506</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136766616</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>136766700</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>136766761</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136766788</v>
       </c>
       <c r="B16" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>136767108</v>
       </c>
       <c r="B17" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>136767179</v>
       </c>
       <c r="B18" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2635,7 @@
         <v>136767358</v>
       </c>
       <c r="B19" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>136767691</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 36159-2026 artfynd.xlsx
+++ b/artfynd/A 36159-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136766121</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136766816</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136767175</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         <v>136766118</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>136766256</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>136767348</v>
       </c>
       <c r="B23" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>136767462</v>
       </c>
       <c r="B24" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
